--- a/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1915,12 +1915,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>AC-17</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Remote Access</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
+          <t>AWS provides the network primitives (Client VPN, Verified Access, Security Groups, IAM) but does not configure or operate the customer's remote-access policy or endpoints.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
+          <t>Customer is responsible for authorizing remote access prior to connection and enforcing approved methods: AWS Client VPN with certificate + IdP authentication, conditional-access rules, session logging to CloudWatch, and periodic review of remote-access entitlements.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PL-4</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Rules of Behavior</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
+          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PM-1</t>
+          <t>PL-4</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Information Security Program Plan</t>
+          <t>Rules of Behavior</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
+          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PM-1</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>Information Security Program Plan</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
+          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2203,62 +2203,94 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Not applicable to AWS GovCloud (US) customer service offering. AWS provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. AWS GovCloud datacenter emergency power implementation is fully internal to AWS facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>

--- a/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1051,27 +1051,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CM-2</t>
+          <t>AU-9</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Baseline Configuration</t>
+          <t>Protection of Audit Information</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains baseline configurations for all AWS-managed infrastructure and AWS-managed services per AWS configuration management policy.</t>
+          <t>AWS provides the durable, encryptable storage primitives (S3 Object Lock for write-once-read-many retention, KMS for at-rest encryption, IAM for access control) but does not configure them on customer buckets.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and maintaining baseline configurations for customer-managed AMIs, container images, RDS parameter groups, and Infrastructure-as-Code templates (CloudFormation, Terraform, CDK). Baselines reviewed and re-approved at minimum annually and after any significant change. Drift detection via AWS Config or equivalent.</t>
+          <t>Customer is responsible for protecting customer audit information: enabling S3 Object Lock (compliance mode) on the audit-log bucket, restricting access via least-privilege IAM policies, and enabling KMS encryption so audit records cannot be modified or deleted.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CM-6</t>
+          <t>CM-2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Configuration Settings</t>
+          <t>Baseline Configuration</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>AWS configures AWS-managed services per AWS security baselines aligned to applicable benchmarks (CIS AWS Foundations, AWS Well-Architected Security Pillar).</t>
+          <t>AWS maintains baseline configurations for all AWS-managed infrastructure and AWS-managed services per AWS configuration management policy.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks at the highest applicable level, (b) enforcing configuration settings continuously via AWS Config managed rules and custom rules, (c) remediating configuration drift within customer-defined SLAs, and (d) documenting any approved deviations from the baseline with compensating controls.</t>
+          <t>Customer is responsible for developing, documenting, and maintaining baseline configurations for customer-managed AMIs, container images, RDS parameter groups, and Infrastructure-as-Code templates (CloudFormation, Terraform, CDK). Baselines reviewed and re-approved at minimum annually and after any significant change. Drift detection via AWS Config or equivalent.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CM-8</t>
+          <t>CM-6</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>System Component Inventory</t>
+          <t>Configuration Settings</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains a complete inventory of all AWS-managed physical and virtual infrastructure supporting the GovCloud service offering.</t>
+          <t>AWS configures AWS-managed services per AWS security baselines aligned to applicable benchmarks (CIS AWS Foundations, AWS Well-Architected Security Pillar).</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for maintaining an accurate, up-to-date inventory of customer-deployed resources via AWS Config, AWS Resource Groups, Systems Manager Inventory, and tag-based resource organization. Inventory accuracy reviewed and reconciled at minimum monthly; new resource types incorporated into inventory within 30 days of first use.</t>
+          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks at the highest applicable level, (b) enforcing configuration settings continuously via AWS Config managed rules and custom rules, (c) remediating configuration drift within customer-defined SLAs, and (d) documenting any approved deviations from the baseline with compensating controls.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CM-9</t>
+          <t>CM-8</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Configuration Management Plan</t>
+          <t>System Component Inventory</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains an AWS-internal configuration management plan governing changes to AWS-managed infrastructure.</t>
+          <t>AWS maintains a complete inventory of all AWS-managed physical and virtual infrastructure supporting the GovCloud service offering.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer-side configuration management plan covering customer-deployed resources, including (a) roles and responsibilities, (b) configuration items under management, (c) change request and approval workflow, (d) integration with customer change advisory board, and (e) coordination with AWS-published change notifications.</t>
+          <t>Customer is responsible for maintaining an accurate, up-to-date inventory of customer-deployed resources via AWS Config, AWS Resource Groups, Systems Manager Inventory, and tag-based resource organization. Inventory accuracy reviewed and reconciled at minimum monthly; new resource types incorporated into inventory within 30 days of first use.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CP-9</t>
+          <t>CM-9</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>System Backup</t>
+          <t>Configuration Management Plan</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>AWS replicates and backs up all AWS-managed control-plane and service data per AWS contingency planning policy. AWS guarantees the durability of S3 standard storage at 99.999999999% (11 nines).</t>
+          <t>AWS maintains an AWS-internal configuration management plan governing changes to AWS-managed infrastructure.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for backing up customer-owned data with backup frequency aligned to customer-defined RPO: AMI snapshots, EBS snapshots, RDS automated backups + cross-region snapshot copies, S3 cross-region replication, DynamoDB point-in-time recovery, and AWS Backup plans for centralized policy-based backup. Backup integrity tested per CP-4.</t>
+          <t>Customer is responsible for developing and maintaining the customer-side configuration management plan covering customer-deployed resources, including (a) roles and responsibilities, (b) configuration items under management, (c) change request and approval workflow, (d) integration with customer change advisory board, and (e) coordination with AWS-published change notifications.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CP-10</t>
+          <t>CP-9</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>System Recovery and Reconstitution</t>
+          <t>System Backup</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>AWS provides multi-AZ and multi-region service availability and service-level reconstitution capabilities. AWS publishes service-level RTO/RPO via the AWS Service Health Dashboard and Personal Health Dashboard.</t>
+          <t>AWS replicates and backs up all AWS-managed control-plane and service data per AWS contingency planning policy. AWS guarantees the durability of S3 standard storage at 99.999999999% (11 nines).</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) designing customer workloads for multi-AZ deployment by default and multi-region deployment for tier-1 systems, (b) documenting customer-defined RTO and RPO per workload, (c) implementing automated failover where supported, and (d) exercising recovery procedures at minimum annually with documented results.</t>
+          <t>Customer is responsible for backing up customer-owned data with backup frequency aligned to customer-defined RPO: AMI snapshots, EBS snapshots, RDS automated backups + cross-region snapshot copies, S3 cross-region replication, DynamoDB point-in-time recovery, and AWS Backup plans for centralized policy-based backup. Backup integrity tested per CP-4.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IA-2</t>
+          <t>CP-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Organizational Users)</t>
+          <t>System Recovery and Reconstitution</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>AWS authenticates AWS personnel via AWS-internal MFA and PIV-equivalent credentials. AWS provides IAM (long-term credentials), IAM Identity Center (federated SSO), and hardware MFA token support for customer use.</t>
+          <t>AWS provides multi-AZ and multi-region service availability and service-level reconstitution capabilities. AWS publishes service-level RTO/RPO via the AWS Service Health Dashboard and Personal Health Dashboard.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing MFA on all customer IAM users, with hardware MFA mandatory for the root account and for principals authorized to perform privileged operations, (b) configuring SAML 2.0 or OIDC federation with the customer enterprise identity provider, (c) rotating IAM access keys at maximum 90-day intervals per IA-5, and (d) enforcing FIPS 140-2 validated authenticators for all government-user access.</t>
+          <t>Customer is responsible for (a) designing customer workloads for multi-AZ deployment by default and multi-region deployment for tier-1 systems, (b) documenting customer-defined RTO and RPO per workload, (c) implementing automated failover where supported, and (d) exercising recovery procedures at minimum annually with documented results.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>IA-5</t>
+          <t>IA-2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Authenticator Management</t>
+          <t>Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>AWS manages authenticators for AWS personnel per AWS Personnel Security policy including initial issuance, rotation, and revocation.</t>
+          <t>AWS authenticates AWS personnel via AWS-internal MFA and PIV-equivalent credentials. AWS provides IAM (long-term credentials), IAM Identity Center (federated SSO), and hardware MFA token support for customer use.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-side authenticators: (a) IAM access key rotation at maximum 90-day intervals, (b) IAM password policy enforcement (minimum 14 characters, complexity, reuse-prevention history, expiration), (c) MFA device lifecycle including loss reporting and re-issuance, and (d) AWS Secrets Manager or Parameter Store rotation schedules for application credentials with automatic rotation enabled.</t>
+          <t>Customer is responsible for (a) enforcing MFA on all customer IAM users, with hardware MFA mandatory for the root account and for principals authorized to perform privileged operations, (b) configuring SAML 2.0 or OIDC federation with the customer enterprise identity provider, (c) rotating IAM access keys at maximum 90-day intervals per IA-5, and (d) enforcing FIPS 140-2 validated authenticators for all government-user access.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IA-8</t>
+          <t>IA-5</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Non-Organizational Users)</t>
+          <t>Authenticator Management</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>AWS provides Amazon Cognito and IAM identity federation services supporting SAML 2.0, OIDC, and social identity providers for non-organizational user authentication to customer applications.</t>
+          <t>AWS manages authenticators for AWS personnel per AWS Personnel Security policy including initial issuance, rotation, and revocation.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for configuring Cognito user pools and identity pools, integrating with approved external identity providers, enforcing MFA on non-organizational users where required by customer policy, and documenting the trust relationships in the customer SSP.</t>
+          <t>Customer is responsible for managing customer-side authenticators: (a) IAM access key rotation at maximum 90-day intervals, (b) IAM password policy enforcement (minimum 14 characters, complexity, reuse-prevention history, expiration), (c) MFA device lifecycle including loss reporting and re-issuance, and (d) AWS Secrets Manager or Parameter Store rotation schedules for application credentials with automatic rotation enabled.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IR-4</t>
+          <t>IA-8</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Incident Handling</t>
+          <t>Identification and Authentication (Non-Organizational Users)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>AWS handles incidents affecting AWS-managed infrastructure per the AWS Incident Response plan and notifies affected customers per the AWS shared responsibility model and the AWS Customer Agreement.</t>
+          <t>AWS provides Amazon Cognito and IAM identity federation services supporting SAML 2.0, OIDC, and social identity providers for non-organizational user authentication to customer applications.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for incident handling within the customer environment: (a) detection via GuardDuty, Security Hub, Macie, and customer SIEM, (b) triage and investigation per customer IR playbooks, (c) containment via IAM revocation, Security Group quarantine, and instance isolation, (d) eradication and recovery per customer IR plan, and (e) breach notification per customer regulatory obligations.</t>
+          <t>Customer is responsible for configuring Cognito user pools and identity pools, integrating with approved external identity providers, enforcing MFA on non-organizational users where required by customer policy, and documenting the trust relationships in the customer SSP.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IR-6</t>
+          <t>IR-4</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>Incident Handling</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AWS reports incidents affecting AWS-managed infrastructure to affected customers and to FedRAMP PMO per AWS incident reporting procedures and the AWS FedRAMP High SSP.</t>
+          <t>AWS handles incidents affecting AWS-managed infrastructure per the AWS Incident Response plan and notifies affected customers per the AWS shared responsibility model and the AWS Customer Agreement.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reporting customer-environment incidents to (a) customer-organization authorities per customer policy, (b) US-CERT per FISMA reporting timeframes, (c) the FedRAMP PMO within 1 hour of incident determination (per FedRAMP Incident Communications Procedure) if the system is FedRAMP-authorized, and (d) any sector-specific regulator (CISA, sector ISAC) as required.</t>
+          <t>Customer is responsible for incident handling within the customer environment: (a) detection via GuardDuty, Security Hub, Macie, and customer SIEM, (b) triage and investigation per customer IR playbooks, (c) containment via IAM revocation, Security Group quarantine, and instance isolation, (d) eradication and recovery per customer IR plan, and (e) breach notification per customer regulatory obligations.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IR-8</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Incident Response Plan</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains an AWS-internal incident response plan for AWS-managed infrastructure, reviewed annually and after lessons-learned activities.</t>
+          <t>AWS reports incidents affecting AWS-managed infrastructure to affected customers and to FedRAMP PMO per AWS incident reporting procedures and the AWS FedRAMP High SSP.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, distributing, and annually reviewing the customer Incident Response Plan covering the customer-deployed environment. Plan must address coordination with AWS for incidents spanning the shared responsibility boundary and must designate the customer point-of-contact for AWS incident notifications.</t>
+          <t>Customer is responsible for reporting customer-environment incidents to (a) customer-organization authorities per customer policy, (b) US-CERT per FISMA reporting timeframes, (c) the FedRAMP PMO within 1 hour of incident determination (per FedRAMP Incident Communications Procedure) if the system is FedRAMP-authorized, and (d) any sector-specific regulator (CISA, sector ISAC) as required.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MA-2</t>
+          <t>IR-8</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Controlled Maintenance</t>
+          <t>Incident Response Plan</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>AWS performs all controlled maintenance on AWS-managed physical infrastructure per AWS change management procedures with documented schedules, approvals, and post-maintenance verification.</t>
+          <t>AWS maintains an AWS-internal incident response plan for AWS-managed infrastructure, reviewed annually and after lessons-learned activities.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for controlled maintenance of customer-managed logical components: guest OS patching, application maintenance, RDS engine version upgrades, container image updates, and Lambda runtime updates. Maintenance scheduled per customer change management with documented approvals and rollback procedures.</t>
+          <t>Customer is responsible for developing, documenting, distributing, and annually reviewing the customer Incident Response Plan covering the customer-deployed environment. Plan must address coordination with AWS for incidents spanning the shared responsibility boundary and must designate the customer point-of-contact for AWS incident notifications.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MA-3</t>
+          <t>MA-2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Tools</t>
+          <t>Controlled Maintenance</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>AWS controls, inspects, and sanitizes all maintenance tools entering AWS datacenter facilities per AWS physical security procedures.</t>
+          <t>AWS performs all controlled maintenance on AWS-managed physical infrastructure per AWS change management procedures with documented schedules, approvals, and post-maintenance verification.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for approving and controlling customer-side maintenance tools used against customer-managed resources, including Systems Manager Run Command documents, Session Manager preferences, third-party EDR maintenance agents, and any customer scripts with elevated privileges.</t>
+          <t>Customer is responsible for controlled maintenance of customer-managed logical components: guest OS patching, application maintenance, RDS engine version upgrades, container image updates, and Lambda runtime updates. Maintenance scheduled per customer change management with documented approvals and rollback procedures.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MA-4</t>
+          <t>MA-3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Nonlocal Maintenance</t>
+          <t>Maintenance Tools</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>AWS authorizes, monitors, and audits all nonlocal maintenance on AWS-managed infrastructure via approved AWS-internal access paths with MFA and full session recording.</t>
+          <t>AWS controls, inspects, and sanitizes all maintenance tools entering AWS datacenter facilities per AWS physical security procedures.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: (a) all administrative access via Systems Manager Session Manager (no direct SSH/RDP), (b) MFA enforced on all administrative sessions, (c) session recording enabled and stored in tamper-resistant S3 with Object Lock, and (d) FIPS-validated transport for all administrative connections.</t>
+          <t>Customer is responsible for approving and controlling customer-side maintenance tools used against customer-managed resources, including Systems Manager Run Command documents, Session Manager preferences, third-party EDR maintenance agents, and any customer scripts with elevated privileges.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MA-5</t>
+          <t>MA-4</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Personnel</t>
+          <t>Nonlocal Maintenance</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AWS maintenance personnel undergo AWS Personnel Security screening per PS-3 (inherited) prior to access authorization.</t>
+          <t>AWS authorizes, monitors, and audits all nonlocal maintenance on AWS-managed infrastructure via approved AWS-internal access paths with MFA and full session recording.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vetting customer personnel authorized to perform maintenance on customer-managed AWS resources: background investigation per customer PS-3, designated maintenance role in IAM, documented authorization, and revocation upon role change or separation.</t>
+          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: (a) all administrative access via Systems Manager Session Manager (no direct SSH/RDP), (b) MFA enforced on all administrative sessions, (c) session recording enabled and stored in tamper-resistant S3 with Object Lock, and (d) FIPS-validated transport for all administrative connections.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SA-9</t>
+          <t>MA-5</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>External System Services</t>
+          <t>Maintenance Personnel</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>AWS provides FedRAMP High authorized services within GovCloud; AWS publishes the FedRAMP authorization package, SOC reports, and ISO certifications via AWS Artifact for customer due-diligence review.</t>
+          <t>AWS maintenance personnel undergo AWS Personnel Security screening per PS-3 (inherited) prior to access authorization.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) assessing external (non-AWS) services used by customer workloads against customer security requirements, (b) documenting all customer-managed third-party connections and the data flows traversing them, (c) ensuring contractual security commitments from third-party providers, and (d) periodic re-assessment of external service authorizations.</t>
+          <t>Customer is responsible for vetting customer personnel authorized to perform maintenance on customer-managed AWS resources: background investigation per customer PS-3, designated maintenance role in IAM, documented authorization, and revocation upon role change or separation.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SC-1</t>
+          <t>SA-9</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>System and Communications Protection Policy and Procedures</t>
+          <t>External System Services</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains AWS-internal system and communications protection policy and procedures applicable to AWS-managed infrastructure, reviewed annually.</t>
+          <t>AWS provides FedRAMP High authorized services within GovCloud; AWS publishes the FedRAMP authorization package, SOC reports, and ISO certifications via AWS Artifact for customer due-diligence review.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and annually reviewing the customer-side system and communications protection policy and procedures, addressing customer-deployed network architecture, encryption requirements, and boundary protection design.</t>
+          <t>Customer is responsible for (a) assessing external (non-AWS) services used by customer workloads against customer security requirements, (b) documenting all customer-managed third-party connections and the data flows traversing them, (c) ensuring contractual security commitments from third-party providers, and (d) periodic re-assessment of external service authorizations.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SC-7</t>
+          <t>SC-1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Boundary Protection</t>
+          <t>System and Communications Protection Policy and Procedures</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>AWS provides VPC, Security Groups, Network ACLs, AWS WAF, AWS Shield, Network Firewall, Transit Gateway, and PrivateLink as boundary protection primitives. AWS protects the AWS service boundary at the service API layer.</t>
+          <t>AWS maintains AWS-internal system and communications protection policy and procedures applicable to AWS-managed infrastructure, reviewed annually.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for designing the customer VPC boundary architecture including (a) public/private subnet segmentation, (b) Security Group rules enforcing least-privilege traffic flows, (c) NACL rules at the subnet boundary, (d) WAF rules on internet-facing ALBs and API Gateway, (e) Network Firewall deployment for VPC-level egress filtering, and (f) enforcement of the customer-defined boundary between trust zones per the customer architecture.</t>
+          <t>Customer is responsible for developing, documenting, and annually reviewing the customer-side system and communications protection policy and procedures, addressing customer-deployed network architecture, encryption requirements, and boundary protection design.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SC-8</t>
+          <t>SC-7</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Transmission Confidentiality and Integrity</t>
+          <t>Boundary Protection</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>AWS encrypts data in transit between AWS services and across AWS regions using TLS 1.2 or higher with FIPS-validated cipher suites. AWS physically protects inter-datacenter dark fiber.</t>
+          <t>AWS provides VPC, Security Groups, Network ACLs, AWS WAF, AWS Shield, Network Firewall, Transit Gateway, and PrivateLink as boundary protection primitives. AWS protects the AWS service boundary at the service API layer.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints (ALB/NLB listeners, API Gateway, CloudFront distributions), (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access via redirect or policy, (d) ensuring application-layer TLS for service-to-service communication, and (e) using FIPS endpoints (-fips. suffix) where the customer system is FedRAMP- or FISMA-regulated.</t>
+          <t>Customer is responsible for designing the customer VPC boundary architecture including (a) public/private subnet segmentation, (b) Security Group rules enforcing least-privilege traffic flows, (c) NACL rules at the subnet boundary, (d) WAF rules on internet-facing ALBs and API Gateway, (e) Network Firewall deployment for VPC-level egress filtering, and (f) enforcement of the customer-defined boundary between trust zones per the customer architecture.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-8</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Key Establishment and Management</t>
+          <t>Transmission Confidentiality and Integrity</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>AWS manages keys for AWS-managed encryption (AWS-owned and AWS-managed KMS keys). AWS provides AWS KMS (FIPS 140-2 Level 2 validated HSMs) and AWS CloudHSM (FIPS 140-2 Level 3 validated single-tenant HSMs) for customer key management.</t>
+          <t>AWS encrypts data in transit between AWS services and across AWS regions using TLS 1.2 or higher with FIPS-validated cipher suites. AWS physically protects inter-datacenter dark fiber.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-managed KMS CMKs and CloudHSM clusters where applicable: (a) key creation with appropriate key spec and usage, (b) automatic annual rotation enabled for symmetric CMKs, (c) IAM and key policies enforcing least-privilege key access, (d) CloudTrail logging of all key usage, and (e) scheduled deletion with appropriate waiting period prior to permanent removal.</t>
+          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints (ALB/NLB listeners, API Gateway, CloudFront distributions), (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access via redirect or policy, (d) ensuring application-layer TLS for service-to-service communication, and (e) using FIPS endpoints (-fips. suffix) where the customer system is FedRAMP- or FISMA-regulated.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Cryptographic Key Establishment and Management</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>AWS provides FIPS 140-2 validated cryptographic modules within GovCloud via AWS KMS (Level 2), AWS CloudHSM (Level 3), AWS Certificate Manager, and FIPS-validated service endpoints. NIAP-approved configurations available per service.</t>
+          <t>AWS manages keys for AWS-managed encryption (AWS-owned and AWS-managed KMS keys). AWS provides AWS KMS (FIPS 140-2 Level 2 validated HSMs) and AWS CloudHSM (FIPS 140-2 Level 3 validated single-tenant HSMs) for customer key management.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for using only FIPS 140-2 validated cryptographic implementations for all customer workloads: (a) enable FIPS service endpoints (-fips. suffix) for all customer service calls, (b) configure FIPS mode in customer EC2 guest operating systems where supported, (c) avoid non-FIPS algorithms in customer applications, and (d) document customer cryptographic implementations in the customer SSP.</t>
+          <t>Customer is responsible for managing customer-managed KMS CMKs and CloudHSM clusters where applicable: (a) key creation with appropriate key spec and usage, (b) automatic annual rotation enabled for symmetric CMKs, (c) IAM and key policies enforcing least-privilege key access, (d) CloudTrail logging of all key usage, and (e) scheduled deletion with appropriate waiting period prior to permanent removal.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SI-2</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Flaw Remediation</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>AWS identifies and remediates flaws in AWS-managed services per AWS Vulnerability Management policy. AWS publishes service-level security bulletins via the AWS Security Bulletins page.</t>
+          <t>AWS provides FIPS 140-2 validated cryptographic modules within GovCloud via AWS KMS (Level 2), AWS CloudHSM (Level 3), AWS Certificate Manager, and FIPS-validated service endpoints. NIAP-approved configurations available per service.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS, container, and application patching via AWS Systems Manager Patch Manager, (b) Inspector findings remediation per customer-defined SLAs, (c) Critical CVEs remediated within 30 days of vendor disclosure, (d) High CVEs within 90 days, (e) CISA Known Exploited Vulnerabilities Catalog entries remediated within the BOD 22-01 mandated timeframe (typically 15 days for federal systems), and (f) documented exception process for any deviation.</t>
+          <t>Customer is responsible for using only FIPS 140-2 validated cryptographic implementations for all customer workloads: (a) enable FIPS service endpoints (-fips. suffix) for all customer service calls, (b) configure FIPS mode in customer EC2 guest operating systems where supported, (c) avoid non-FIPS algorithms in customer applications, and (d) document customer cryptographic implementations in the customer SSP.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SI-3</t>
+          <t>SI-2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Malicious Code Protection</t>
+          <t>Flaw Remediation</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>AWS protects AWS-managed infrastructure against malicious code via AWS-internal endpoint protection and AWS-internal SOC monitoring.</t>
+          <t>AWS identifies and remediates flaws in AWS-managed services per AWS Vulnerability Management policy. AWS publishes service-level security bulletins via the AWS Security Bulletins page.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for deploying malicious code protection on customer workloads: (a) anti-malware on customer EC2 / EKS / ECS workloads via vendor EDR or ClamAV, (b) Amazon GuardDuty Malware Protection enabled across all accounts, (c) signature and engine updates within 24 hours of vendor release, and (d) remediation of detections per customer IR-4.</t>
+          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS, container, and application patching via AWS Systems Manager Patch Manager, (b) Inspector findings remediation per customer-defined SLAs, (c) Critical CVEs remediated within 30 days of vendor disclosure, (d) High CVEs within 90 days, (e) CISA Known Exploited Vulnerabilities Catalog entries remediated within the BOD 22-01 mandated timeframe (typically 15 days for federal systems), and (f) documented exception process for any deviation.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SI-4</t>
+          <t>SI-3</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>System Monitoring</t>
+          <t>Malicious Code Protection</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>AWS monitors AWS-managed infrastructure via AWS-internal SOC tooling with 24x7 coverage and automated alerting.</t>
+          <t>AWS protects AWS-managed infrastructure against malicious code via AWS-internal endpoint protection and AWS-internal SOC monitoring.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for monitoring customer-deployed workloads via (a) CloudWatch metrics and alarms, (b) Amazon GuardDuty across all accounts and regions, (c) AWS Security Hub for cross-service finding aggregation, (d) AWS Inspector for vulnerability assessment, (e) Amazon Macie for sensitive-data discovery in S3, and (f) customer SIEM integration via Kinesis Data Firehose or partner connector. Alerts triaged per IR-4.</t>
+          <t>Customer is responsible for deploying malicious code protection on customer workloads: (a) anti-malware on customer EC2 / EKS / ECS workloads via vendor EDR or ClamAV, (b) Amazon GuardDuty Malware Protection enabled across all accounts, (c) signature and engine updates within 24 hours of vendor release, and (d) remediation of detections per customer IR-4.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MP-4</t>
+          <t>SI-4</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Media Storage</t>
+          <t>System Monitoring</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>AWS physically secures and controls access to storage media within AWS datacenter facilities per AWS Physical Security policy.</t>
+          <t>AWS monitors AWS-managed infrastructure via AWS-internal SOC tooling with 24x7 coverage and automated alerting.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for protecting customer logical media: (a) data classification labeling via S3 object tags, (b) S3 bucket policies denying public access with S3 Block Public Access at account and bucket level, (c) encryption-at-rest for all customer media (EBS, S3, RDS, DynamoDB) using customer-managed KMS keys, and (d) MFA Delete on critical S3 buckets.</t>
+          <t>Customer is responsible for monitoring customer-deployed workloads via (a) CloudWatch metrics and alarms, (b) Amazon GuardDuty across all accounts and regions, (c) AWS Security Hub for cross-service finding aggregation, (d) AWS Inspector for vulnerability assessment, (e) Amazon Macie for sensitive-data discovery in S3, and (f) customer SIEM integration via Kinesis Data Firehose or partner connector. Alerts triaged per IR-4.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MP-6</t>
+          <t>MP-4</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Media Sanitization</t>
+          <t>Media Storage</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>AWS sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 guidelines including degaussing, shredding, or pulverization with documented certificates of destruction.</t>
+          <t>AWS physically secures and controls access to storage media within AWS datacenter facilities per AWS Physical Security policy.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for sanitizing customer-managed data: (a) EBS volume deletion (KMS key deletion = NIST 800-88 cryptographic erasure when customer-managed CMK is used), (b) emptying versioned S3 buckets including all noncurrent versions and delete markers, (c) RDS snapshot deletion, and (d) scheduled deletion of customer-managed KMS CMKs that encrypted retired data.</t>
+          <t>Customer is responsible for protecting customer logical media: (a) data classification labeling via S3 object tags, (b) S3 bucket policies denying public access with S3 Block Public Access at account and bucket level, (c) encryption-at-rest for all customer media (EBS, S3, RDS, DynamoDB) using customer-managed KMS keys, and (d) MFA Delete on critical S3 buckets.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1915,27 +1915,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AC-17</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Remote Access</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>AWS provides the network primitives (Client VPN, Verified Access, Security Groups, IAM) but does not configure or operate the customer's remote-access policy or endpoints.</t>
+          <t>AWS sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 guidelines including degaussing, shredding, or pulverization with documented certificates of destruction.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for authorizing remote access prior to connection and enforcing approved methods: AWS Client VPN with certificate + IdP authentication, conditional-access rules, session logging to CloudWatch, and periodic review of remote-access entitlements.</t>
+          <t>Customer is responsible for sanitizing customer-managed data: (a) EBS volume deletion (KMS key deletion = NIST 800-88 cryptographic erasure when customer-managed CMK is used), (b) emptying versioned S3 buckets including all noncurrent versions and delete markers, (c) RDS snapshot deletion, and (d) scheduled deletion of customer-managed KMS CMKs that encrypted retired data.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>AC-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Remote Access</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
+          <t>AWS provides the network primitives (Client VPN, Verified Access, Security Groups, IAM) but does not configure or operate the customer's remote-access policy or endpoints.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
+          <t>Customer is responsible for authorizing remote access prior to connection and enforcing approved methods: AWS Client VPN with certificate + IdP authentication, conditional-access rules, session logging to CloudWatch, and periodic review of remote-access entitlements.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PL-4</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Rules of Behavior</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
+          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PM-1</t>
+          <t>PL-4</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Information Security Program Plan</t>
+          <t>Rules of Behavior</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
+          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PM-1</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>Information Security Program Plan</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
+          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2235,62 +2235,94 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Not applicable to AWS GovCloud (US) customer service offering. AWS provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. AWS GovCloud datacenter emergency power implementation is fully internal to AWS facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>

--- a/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
@@ -1925,22 +1925,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>AWS sanitizes decommissioned physical storage media per NIST SP 800-88 Rev. 1 guidelines including degaussing, shredding, or pulverization with documented certificates of destruction.</t>
+          <t>Not applicable to the AWS GovCloud customer service offering for this system: AWS performs NIST SP 800-88 cryptographic erasure of the customer-managed storage media plane (EBS/S3 key destruction) as a provider operation; there is no separate customer media-sanitization action on this enclave.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for sanitizing customer-managed data: (a) EBS volume deletion (KMS key deletion = NIST 800-88 cryptographic erasure when customer-managed CMK is used), (b) emptying versioned S3 buckets including all noncurrent versions and delete markers, (c) RDS snapshot deletion, and (d) scheduled deletion of customer-managed KMS CMKs that encrypted retired data.</t>
+          <t>Not applicable to customer on AWS GovCloud. The customer retains no media-sanitization implementation or compensating-control responsibility for this enclave; sanitization is provider-performed via cryptographic erasure.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Not Implemented</t>
         </is>
       </c>
     </row>

--- a/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
+++ b/demo/crm/AWS_GovCloud_FedRAMP_High_CRM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PE-6</t>
+          <t>PE-8</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Monitoring Physical Access</t>
+          <t>Visitor Access Records</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AWS monitors physical access to AWS datacenter facilities via (1) CCTV coverage of all access points with minimum 90-day retention, (2) intrusion detection sensors at all perimeter and internal access boundaries, (3) continuous review by AWS Security Operations Center, and (4) automated alerting on anomalous access patterns.</t>
+          <t>AWS maintains visitor access records for all AWS datacenter facilities, capturing visitor identity, escort, purpose, and entry/exit timestamps. Records are retained and reviewed per AWS facility-security procedures.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits AWS physical access monitoring. Customer may review the AWS SOC 2 Type II and FedRAMP High audit reports via AWS Artifact for assurance evidence.</t>
+          <t>Customer fully inherits AWS datacenter visitor access records. Customer personnel are not granted physical access to AWS GovCloud datacenters, so there is no customer-side cloud visitor log. The customer remains responsible for visitor access records at any customer-operated on-premises facility hosting the system's flex footprint.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -603,12 +603,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PE-12</t>
+          <t>PE-6</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Emergency Lighting</t>
+          <t>Monitoring Physical Access</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AWS datacenters provide and maintain emergency lighting throughout facility egress paths and operational areas. Emergency lighting is powered by UPS-backed circuits with monthly inspection and testing per NFPA 101 Life Safety Code.</t>
+          <t>AWS monitors physical access to AWS datacenter facilities via (1) CCTV coverage of all access points with minimum 90-day retention, (2) intrusion detection sensors at all perimeter and internal access boundaries, (3) continuous review by AWS Security Operations Center, and (4) automated alerting on anomalous access patterns.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits AWS datacenter emergency lighting controls. No customer-side implementation responsibility.</t>
+          <t>Customer fully inherits AWS physical access monitoring. Customer may review the AWS SOC 2 Type II and FedRAMP High audit reports via AWS Artifact for assurance evidence.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PE-13</t>
+          <t>PE-12</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Emergency Lighting</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AWS datacenters deploy (1) VESDA (Very Early Smoke Detection Apparatus) for early-warning detection, (2) pre-action dry-pipe fire suppression systems, (3) handheld extinguishers per NFPA 10, and (4) quarterly inspection and annual recertification of all suppression equipment.</t>
+          <t>AWS datacenters provide and maintain emergency lighting throughout facility egress paths and operational areas. Emergency lighting is powered by UPS-backed circuits with monthly inspection and testing per NFPA 101 Life Safety Code.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits AWS datacenter fire protection. Customer-managed AMIs, EBS volumes, and S3 data are protected against facility-level fire events through customer-implemented multi-AZ / multi-region replication per CP-9.</t>
+          <t>Customer fully inherits AWS datacenter emergency lighting controls. No customer-side implementation responsibility.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PE-14</t>
+          <t>PE-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Environmental Controls</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains datacenter temperature and humidity within ASHRAE TC 9.9 recommended ranges via N+1 redundant HVAC systems with continuous monitoring and automated failover. Environmental parameters are logged and reviewed by AWS facility operations.</t>
+          <t>AWS datacenters deploy (1) VESDA (Very Early Smoke Detection Apparatus) for early-warning detection, (2) pre-action dry-pipe fire suppression systems, (3) handheld extinguishers per NFPA 10, and (4) quarterly inspection and annual recertification of all suppression equipment.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Customer fully inherits AWS datacenter environmental controls. No customer-side implementation responsibility.</t>
+          <t>Customer fully inherits AWS datacenter fire protection. Customer-managed AMIs, EBS volumes, and S3 data are protected against facility-level fire events through customer-implemented multi-AZ / multi-region replication per CP-9.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -699,27 +699,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PE-4</t>
+          <t>PE-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Transmission</t>
+          <t>Environmental Controls</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Service Provider</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>AWS controls physical access to all information system distribution and transmission lines within AWS datacenter facilities, including all intra-facility fiber, copper, and power distribution.</t>
+          <t>AWS maintains datacenter temperature and humidity within ASHRAE TC 9.9 recommended ranges via N+1 redundant HVAC systems with continuous monitoring and automated failover. Environmental parameters are logged and reviewed by AWS facility operations.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer has no role in physical transmission line access control within AWS datacenter facilities and no compensating-control responsibility.</t>
+          <t>Customer fully inherits AWS datacenter environmental controls. No customer-side implementation responsibility.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PE-5</t>
+          <t>PE-4</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Access Control for Output Devices</t>
+          <t>Access Control for Transmission</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AWS controls physical access to output devices (printers, displays, console monitors) within AWS datacenter facilities. AWS does not provide physical output devices to customers; all customer interaction with the service occurs via authenticated remote APIs.</t>
+          <t>AWS controls physical access to all information system distribution and transmission lines within AWS datacenter facilities, including all intra-facility fiber, copper, and power distribution.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Provider-owned. Customer does not maintain physical output devices in AWS facilities. Not applicable to customer.</t>
+          <t>Provider-owned. Customer has no role in physical transmission line access control within AWS datacenter facilities and no compensating-control responsibility.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -763,27 +763,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AC-1</t>
+          <t>PE-5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Access Control Policy and Procedures</t>
+          <t>Access Control for Output Devices</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Service Provider</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>AWS develops, documents, and reviews AWS-internal access control policy and procedures applicable to AWS personnel and AWS-managed infrastructure annually.</t>
+          <t>AWS controls physical access to output devices (printers, displays, console monitors) within AWS datacenter facilities. AWS does not provide physical output devices to customers; all customer interaction with the service occurs via authenticated remote APIs.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy and supporting procedures governing customer use of AWS services and customer-deployed workloads. Customer SSP must document the customer's AC-1 policy and its alignment with the customer organization's mission.</t>
+          <t>Provider-owned. Customer does not maintain physical output devices in AWS facilities. Not applicable to customer.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AC-2</t>
+          <t>AC-1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Account Management</t>
+          <t>Access Control Policy and Procedures</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AWS manages the AWS root master account and AWS-internal personnel accounts per AWS Personnel Security policy. AWS provides IAM, IAM Identity Center (formerly SSO), Organizations, and Cognito as account management primitives for customer use.</t>
+          <t>AWS develops, documents, and reviews AWS-internal access control policy and procedures applicable to AWS personnel and AWS-managed infrastructure annually.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for the full lifecycle management of customer-side IAM users, IAM roles, federated identities, and root account credentials, including: (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via IAM Access Analyzer and Access Advisor, (d) automated disabling of IAM users inactive &gt;=90 days, and (e) MFA enforcement on the root account.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, and annually reviewing the customer-side access control policy and supporting procedures governing customer use of AWS services and customer-deployed workloads. Customer SSP must document the customer's AC-1 policy and its alignment with the customer organization's mission.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AC-3</t>
+          <t>AC-2</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Access Enforcement</t>
+          <t>Account Management</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AWS enforces access at the AWS service API layer via IAM policy evaluation; AWS denies all requests not explicitly authorized by an applicable IAM policy, resource policy, SCP, or session policy.</t>
+          <t>AWS manages the AWS root master account and AWS-internal personnel accounts per AWS Personnel Security policy. AWS provides IAM, IAM Identity Center (formerly SSO), Organizations, and Cognito as account management primitives for customer use.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for authoring and maintaining IAM identity-based policies, resource-based policies, Service Control Policies, permission boundaries, and session policies that enforce least-privilege access to customer-owned resources. Customer must validate effective permissions with IAM Policy Simulator and IAM Access Analyzer prior to deployment.</t>
+          <t>Customer is responsible for the full lifecycle management of customer-side IAM users, IAM roles, federated identities, and root account credentials, including: (a) provisioning per documented request/approval workflow, (b) deprovisioning within 24 hours of role change or separation, (c) quarterly access reviews via IAM Access Analyzer and Access Advisor, (d) automated disabling of IAM users inactive &gt;=90 days, and (e) MFA enforcement on the root account.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AC-5</t>
+          <t>AC-3</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Separation of Duties</t>
+          <t>Access Enforcement</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>AWS enforces separation of duties across AWS personnel roles (operations, security, audit) per AWS Personnel Security policy. AWS personnel cannot unilaterally bypass change-management or audit-review controls.</t>
+          <t>AWS enforces access at the AWS service API layer via IAM policy evaluation; AWS denies all requests not explicitly authorized by an applicable IAM policy, resource policy, SCP, or session policy.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for documenting customer-side separation of duties and enforcing the separation via IAM (distinct roles for developers, operators, security engineers, auditors), Service Control Policies that prevent any single principal from both modifying audit logs and performing the actions being audited, and permission boundaries that bound delegated IAM administration.</t>
+          <t>Customer is responsible for authoring and maintaining IAM identity-based policies, resource-based policies, Service Control Policies, permission boundaries, and session policies that enforce least-privilege access to customer-owned resources. Customer must validate effective permissions with IAM Policy Simulator and IAM Access Analyzer prior to deployment.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AC-6</t>
+          <t>AC-5</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Least Privilege</t>
+          <t>Separation of Duties</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AWS implements least privilege for AWS personnel and AWS-managed service-linked roles via narrowly scoped IAM policies.</t>
+          <t>AWS enforces separation of duties across AWS personnel roles (operations, security, audit) per AWS Personnel Security policy. AWS personnel cannot unilaterally bypass change-management or audit-review controls.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for implementing least privilege within customer AWS accounts: (a) IAM policies scoped to the minimum actions and resources required, (b) periodic IAM Access Analyzer findings review and remediation, (c) removal of unused IAM permissions and credentials per Access Advisor, and (d) just-in-time elevation for privileged operations via IAM Identity Center.</t>
+          <t>Customer is responsible for documenting customer-side separation of duties and enforcing the separation via IAM (distinct roles for developers, operators, security engineers, auditors), Service Control Policies that prevent any single principal from both modifying audit logs and performing the actions being audited, and permission boundaries that bound delegated IAM administration.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AU-1</t>
+          <t>AC-6</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Audit and Accountability Policy and Procedures</t>
+          <t>Least Privilege</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>AWS develops and maintains AWS-internal audit and accountability policy for AWS-managed infrastructure, reviewed annually.</t>
+          <t>AWS implements least privilege for AWS personnel and AWS-managed service-linked roles via narrowly scoped IAM policies.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer-side audit and accountability policy and procedures, including the specification of auditable events (per AU-2), retention duration (per AU-11), and review cadence (per AU-6) for customer-deployed workloads.</t>
+          <t>Customer is responsible for implementing least privilege within customer AWS accounts: (a) IAM policies scoped to the minimum actions and resources required, (b) periodic IAM Access Analyzer findings review and remediation, (c) removal of unused IAM permissions and credentials per Access Advisor, and (d) just-in-time elevation for privileged operations via IAM Identity Center.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -955,12 +955,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AU-2</t>
+          <t>AU-1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Event Logging</t>
+          <t>Audit and Accountability Policy and Procedures</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>AWS logs all API calls to AWS-internal infrastructure via AWS-internal audit systems. AWS provides CloudTrail (management events, data events, Insights events), VPC Flow Logs, ELB access logs, S3 server access logs, and CloudWatch Logs for customer event capture.</t>
+          <t>AWS develops and maintains AWS-internal audit and accountability policy for AWS-managed infrastructure, reviewed annually.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enabling CloudTrail in all regions and accounts including organization-wide multi-region trails, (b) enabling data-event logging on customer-sensitive S3 buckets and Lambda functions, (c) configuring CloudWatch Logs for application-level events, and (d) documenting the customer-defined list of auditable event types in the customer SSP per the customer AU-1 policy.</t>
+          <t>Customer is responsible for developing and maintaining the customer-side audit and accountability policy and procedures, including the specification of auditable events (per AU-2), retention duration (per AU-11), and review cadence (per AU-6) for customer-deployed workloads.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -987,12 +987,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AU-6</t>
+          <t>AU-2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Review, Analysis, and Reporting</t>
+          <t>Event Logging</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AWS reviews AWS-internal audit logs continuously via AWS Security Operations Center tooling and reports relevant findings to customers per the AWS shared responsibility model and IR-6 communications.</t>
+          <t>AWS logs all API calls to AWS-internal infrastructure via AWS-internal audit systems. AWS provides CloudTrail (management events, data events, Insights events), VPC Flow Logs, ELB access logs, S3 server access logs, and CloudWatch Logs for customer event capture.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reviewing customer CloudTrail events, VPC Flow Logs, GuardDuty findings, Security Hub findings, Macie alerts, and application-layer audit logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). Findings reportable per IR-6 must be escalated within customer-defined timeframes.</t>
+          <t>Customer is responsible for (a) enabling CloudTrail in all regions and accounts including organization-wide multi-region trails, (b) enabling data-event logging on customer-sensitive S3 buckets and Lambda functions, (c) configuring CloudWatch Logs for application-level events, and (d) documenting the customer-defined list of auditable event types in the customer SSP per the customer AU-1 policy.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AU-12</t>
+          <t>AU-6</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Audit Record Generation</t>
+          <t>Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>AWS generates audit records for all AWS API calls, management-plane events, and AWS-internal service interactions per AWS audit policy.</t>
+          <t>AWS reviews AWS-internal audit logs continuously via AWS Security Operations Center tooling and reports relevant findings to customers per the AWS shared responsibility model and IR-6 communications.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems including (a) EC2 guest OS auditd / Windows Event Log, (b) RDS database audit logs, (c) container runtime logs, and (d) application-layer logs, ensuring records cover the AU-2 event types and are forwarded to a tamper-resistant store (CloudWatch Logs / S3 with Object Lock).</t>
+          <t>Customer is responsible for reviewing customer CloudTrail events, VPC Flow Logs, GuardDuty findings, Security Hub findings, Macie alerts, and application-layer audit logs on the customer-defined cadence (minimum weekly for non-critical, continuous for critical). Findings reportable per IR-6 must be escalated within customer-defined timeframes.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1051,27 +1051,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AU-9</t>
+          <t>AU-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Protection of Audit Information</t>
+          <t>Audit Record Generation</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>AWS provides the durable, encryptable storage primitives (S3 Object Lock for write-once-read-many retention, KMS for at-rest encryption, IAM for access control) but does not configure them on customer buckets.</t>
+          <t>AWS generates audit records for all AWS API calls, management-plane events, and AWS-internal service interactions per AWS audit policy.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for protecting customer audit information: enabling S3 Object Lock (compliance mode) on the audit-log bucket, restricting access via least-privilege IAM policies, and enabling KMS encryption so audit records cannot be modified or deleted.</t>
+          <t>Customer is responsible for enabling audit record generation on all customer-deployed systems including (a) EC2 guest OS auditd / Windows Event Log, (b) RDS database audit logs, (c) container runtime logs, and (d) application-layer logs, ensuring records cover the AU-2 event types and are forwarded to a tamper-resistant store (CloudWatch Logs / S3 with Object Lock).</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1083,27 +1083,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CM-2</t>
+          <t>AU-9</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Baseline Configuration</t>
+          <t>Protection of Audit Information</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains baseline configurations for all AWS-managed infrastructure and AWS-managed services per AWS configuration management policy.</t>
+          <t>AWS provides the durable, encryptable storage primitives (S3 Object Lock for write-once-read-many retention, KMS for at-rest encryption, IAM for access control) but does not configure them on customer buckets.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and maintaining baseline configurations for customer-managed AMIs, container images, RDS parameter groups, and Infrastructure-as-Code templates (CloudFormation, Terraform, CDK). Baselines reviewed and re-approved at minimum annually and after any significant change. Drift detection via AWS Config or equivalent.</t>
+          <t>Customer is responsible for protecting customer audit information: enabling S3 Object Lock (compliance mode) on the audit-log bucket, restricting access via least-privilege IAM policies, and enabling KMS encryption so audit records cannot be modified or deleted.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CM-6</t>
+          <t>CM-2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Configuration Settings</t>
+          <t>Baseline Configuration</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>AWS configures AWS-managed services per AWS security baselines aligned to applicable benchmarks (CIS AWS Foundations, AWS Well-Architected Security Pillar).</t>
+          <t>AWS maintains baseline configurations for all AWS-managed infrastructure and AWS-managed services per AWS configuration management policy.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks at the highest applicable level, (b) enforcing configuration settings continuously via AWS Config managed rules and custom rules, (c) remediating configuration drift within customer-defined SLAs, and (d) documenting any approved deviations from the baseline with compensating controls.</t>
+          <t>Customer is responsible for developing, documenting, and maintaining baseline configurations for customer-managed AMIs, container images, RDS parameter groups, and Infrastructure-as-Code templates (CloudFormation, Terraform, CDK). Baselines reviewed and re-approved at minimum annually and after any significant change. Drift detection via AWS Config or equivalent.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CM-8</t>
+          <t>CM-6</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>System Component Inventory</t>
+          <t>Configuration Settings</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains a complete inventory of all AWS-managed physical and virtual infrastructure supporting the GovCloud service offering.</t>
+          <t>AWS configures AWS-managed services per AWS security baselines aligned to applicable benchmarks (CIS AWS Foundations, AWS Well-Architected Security Pillar).</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for maintaining an accurate, up-to-date inventory of customer-deployed resources via AWS Config, AWS Resource Groups, Systems Manager Inventory, and tag-based resource organization. Inventory accuracy reviewed and reconciled at minimum monthly; new resource types incorporated into inventory within 30 days of first use.</t>
+          <t>Customer is responsible for (a) hardening customer-managed OS images per DISA STIG or CIS Benchmarks at the highest applicable level, (b) enforcing configuration settings continuously via AWS Config managed rules and custom rules, (c) remediating configuration drift within customer-defined SLAs, and (d) documenting any approved deviations from the baseline with compensating controls.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1179,12 +1179,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CM-9</t>
+          <t>CM-8</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Configuration Management Plan</t>
+          <t>System Component Inventory</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains an AWS-internal configuration management plan governing changes to AWS-managed infrastructure.</t>
+          <t>AWS maintains a complete inventory of all AWS-managed physical and virtual infrastructure supporting the GovCloud service offering.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and maintaining the customer-side configuration management plan covering customer-deployed resources, including (a) roles and responsibilities, (b) configuration items under management, (c) change request and approval workflow, (d) integration with customer change advisory board, and (e) coordination with AWS-published change notifications.</t>
+          <t>Customer is responsible for maintaining an accurate, up-to-date inventory of customer-deployed resources via AWS Config, AWS Resource Groups, Systems Manager Inventory, and tag-based resource organization. Inventory accuracy reviewed and reconciled at minimum monthly; new resource types incorporated into inventory within 30 days of first use.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CP-9</t>
+          <t>CM-9</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>System Backup</t>
+          <t>Configuration Management Plan</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>AWS replicates and backs up all AWS-managed control-plane and service data per AWS contingency planning policy. AWS guarantees the durability of S3 standard storage at 99.999999999% (11 nines).</t>
+          <t>AWS maintains an AWS-internal configuration management plan governing changes to AWS-managed infrastructure.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for backing up customer-owned data with backup frequency aligned to customer-defined RPO: AMI snapshots, EBS snapshots, RDS automated backups + cross-region snapshot copies, S3 cross-region replication, DynamoDB point-in-time recovery, and AWS Backup plans for centralized policy-based backup. Backup integrity tested per CP-4.</t>
+          <t>Customer is responsible for developing and maintaining the customer-side configuration management plan covering customer-deployed resources, including (a) roles and responsibilities, (b) configuration items under management, (c) change request and approval workflow, (d) integration with customer change advisory board, and (e) coordination with AWS-published change notifications.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CP-10</t>
+          <t>CP-9</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>System Recovery and Reconstitution</t>
+          <t>System Backup</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>AWS provides multi-AZ and multi-region service availability and service-level reconstitution capabilities. AWS publishes service-level RTO/RPO via the AWS Service Health Dashboard and Personal Health Dashboard.</t>
+          <t>AWS replicates and backs up all AWS-managed control-plane and service data per AWS contingency planning policy. AWS guarantees the durability of S3 standard storage at 99.999999999% (11 nines).</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) designing customer workloads for multi-AZ deployment by default and multi-region deployment for tier-1 systems, (b) documenting customer-defined RTO and RPO per workload, (c) implementing automated failover where supported, and (d) exercising recovery procedures at minimum annually with documented results.</t>
+          <t>Customer is responsible for backing up customer-owned data with backup frequency aligned to customer-defined RPO: AMI snapshots, EBS snapshots, RDS automated backups + cross-region snapshot copies, S3 cross-region replication, DynamoDB point-in-time recovery, and AWS Backup plans for centralized policy-based backup. Backup integrity tested per CP-4.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>IA-2</t>
+          <t>CP-10</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Organizational Users)</t>
+          <t>System Recovery and Reconstitution</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>AWS authenticates AWS personnel via AWS-internal MFA and PIV-equivalent credentials. AWS provides IAM (long-term credentials), IAM Identity Center (federated SSO), and hardware MFA token support for customer use.</t>
+          <t>AWS provides multi-AZ and multi-region service availability and service-level reconstitution capabilities. AWS publishes service-level RTO/RPO via the AWS Service Health Dashboard and Personal Health Dashboard.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing MFA on all customer IAM users, with hardware MFA mandatory for the root account and for principals authorized to perform privileged operations, (b) configuring SAML 2.0 or OIDC federation with the customer enterprise identity provider, (c) rotating IAM access keys at maximum 90-day intervals per IA-5, and (d) enforcing FIPS 140-2 validated authenticators for all government-user access.</t>
+          <t>Customer is responsible for (a) designing customer workloads for multi-AZ deployment by default and multi-region deployment for tier-1 systems, (b) documenting customer-defined RTO and RPO per workload, (c) implementing automated failover where supported, and (d) exercising recovery procedures at minimum annually with documented results.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IA-5</t>
+          <t>IA-2</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Authenticator Management</t>
+          <t>Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>AWS manages authenticators for AWS personnel per AWS Personnel Security policy including initial issuance, rotation, and revocation.</t>
+          <t>AWS authenticates AWS personnel via AWS-internal MFA and PIV-equivalent credentials. AWS provides IAM (long-term credentials), IAM Identity Center (federated SSO), and hardware MFA token support for customer use.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-side authenticators: (a) IAM access key rotation at maximum 90-day intervals, (b) IAM password policy enforcement (minimum 14 characters, complexity, reuse-prevention history, expiration), (c) MFA device lifecycle including loss reporting and re-issuance, and (d) AWS Secrets Manager or Parameter Store rotation schedules for application credentials with automatic rotation enabled.</t>
+          <t>Customer is responsible for (a) enforcing MFA on all customer IAM users, with hardware MFA mandatory for the root account and for principals authorized to perform privileged operations, (b) configuring SAML 2.0 or OIDC federation with the customer enterprise identity provider, (c) rotating IAM access keys at maximum 90-day intervals per IA-5, and (d) enforcing FIPS 140-2 validated authenticators for all government-user access.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IA-8</t>
+          <t>IA-5</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Identification and Authentication (Non-Organizational Users)</t>
+          <t>Authenticator Management</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>AWS provides Amazon Cognito and IAM identity federation services supporting SAML 2.0, OIDC, and social identity providers for non-organizational user authentication to customer applications.</t>
+          <t>AWS manages authenticators for AWS personnel per AWS Personnel Security policy including initial issuance, rotation, and revocation.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for configuring Cognito user pools and identity pools, integrating with approved external identity providers, enforcing MFA on non-organizational users where required by customer policy, and documenting the trust relationships in the customer SSP.</t>
+          <t>Customer is responsible for managing customer-side authenticators: (a) IAM access key rotation at maximum 90-day intervals, (b) IAM password policy enforcement (minimum 14 characters, complexity, reuse-prevention history, expiration), (c) MFA device lifecycle including loss reporting and re-issuance, and (d) AWS Secrets Manager or Parameter Store rotation schedules for application credentials with automatic rotation enabled.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IR-4</t>
+          <t>IA-8</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Incident Handling</t>
+          <t>Identification and Authentication (Non-Organizational Users)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AWS handles incidents affecting AWS-managed infrastructure per the AWS Incident Response plan and notifies affected customers per the AWS shared responsibility model and the AWS Customer Agreement.</t>
+          <t>AWS provides Amazon Cognito and IAM identity federation services supporting SAML 2.0, OIDC, and social identity providers for non-organizational user authentication to customer applications.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for incident handling within the customer environment: (a) detection via GuardDuty, Security Hub, Macie, and customer SIEM, (b) triage and investigation per customer IR playbooks, (c) containment via IAM revocation, Security Group quarantine, and instance isolation, (d) eradication and recovery per customer IR plan, and (e) breach notification per customer regulatory obligations.</t>
+          <t>Customer is responsible for configuring Cognito user pools and identity pools, integrating with approved external identity providers, enforcing MFA on non-organizational users where required by customer policy, and documenting the trust relationships in the customer SSP.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1403,12 +1403,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IR-6</t>
+          <t>IR-4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>Incident Handling</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AWS reports incidents affecting AWS-managed infrastructure to affected customers and to FedRAMP PMO per AWS incident reporting procedures and the AWS FedRAMP High SSP.</t>
+          <t>AWS handles incidents affecting AWS-managed infrastructure per the AWS Incident Response plan and notifies affected customers per the AWS shared responsibility model and the AWS Customer Agreement.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for reporting customer-environment incidents to (a) customer-organization authorities per customer policy, (b) US-CERT per FISMA reporting timeframes, (c) the FedRAMP PMO within 1 hour of incident determination (per FedRAMP Incident Communications Procedure) if the system is FedRAMP-authorized, and (d) any sector-specific regulator (CISA, sector ISAC) as required.</t>
+          <t>Customer is responsible for incident handling within the customer environment: (a) detection via GuardDuty, Security Hub, Macie, and customer SIEM, (b) triage and investigation per customer IR playbooks, (c) containment via IAM revocation, Security Group quarantine, and instance isolation, (d) eradication and recovery per customer IR plan, and (e) breach notification per customer regulatory obligations.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>IR-8</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Incident Response Plan</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains an AWS-internal incident response plan for AWS-managed infrastructure, reviewed annually and after lessons-learned activities.</t>
+          <t>AWS reports incidents affecting AWS-managed infrastructure to affected customers and to FedRAMP PMO per AWS incident reporting procedures and the AWS FedRAMP High SSP.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, distributing, and annually reviewing the customer Incident Response Plan covering the customer-deployed environment. Plan must address coordination with AWS for incidents spanning the shared responsibility boundary and must designate the customer point-of-contact for AWS incident notifications.</t>
+          <t>Customer is responsible for reporting customer-environment incidents to (a) customer-organization authorities per customer policy, (b) US-CERT per FISMA reporting timeframes, (c) the FedRAMP PMO within 1 hour of incident determination (per FedRAMP Incident Communications Procedure) if the system is FedRAMP-authorized, and (d) any sector-specific regulator (CISA, sector ISAC) as required.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MA-2</t>
+          <t>IR-8</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Controlled Maintenance</t>
+          <t>Incident Response Plan</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>AWS performs all controlled maintenance on AWS-managed physical infrastructure per AWS change management procedures with documented schedules, approvals, and post-maintenance verification.</t>
+          <t>AWS maintains an AWS-internal incident response plan for AWS-managed infrastructure, reviewed annually and after lessons-learned activities.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for controlled maintenance of customer-managed logical components: guest OS patching, application maintenance, RDS engine version upgrades, container image updates, and Lambda runtime updates. Maintenance scheduled per customer change management with documented approvals and rollback procedures.</t>
+          <t>Customer is responsible for developing, documenting, distributing, and annually reviewing the customer Incident Response Plan covering the customer-deployed environment. Plan must address coordination with AWS for incidents spanning the shared responsibility boundary and must designate the customer point-of-contact for AWS incident notifications.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MA-3</t>
+          <t>MA-2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Tools</t>
+          <t>Controlled Maintenance</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>AWS controls, inspects, and sanitizes all maintenance tools entering AWS datacenter facilities per AWS physical security procedures.</t>
+          <t>AWS performs all controlled maintenance on AWS-managed physical infrastructure per AWS change management procedures with documented schedules, approvals, and post-maintenance verification.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for approving and controlling customer-side maintenance tools used against customer-managed resources, including Systems Manager Run Command documents, Session Manager preferences, third-party EDR maintenance agents, and any customer scripts with elevated privileges.</t>
+          <t>Customer is responsible for controlled maintenance of customer-managed logical components: guest OS patching, application maintenance, RDS engine version upgrades, container image updates, and Lambda runtime updates. Maintenance scheduled per customer change management with documented approvals and rollback procedures.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MA-4</t>
+          <t>MA-3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Nonlocal Maintenance</t>
+          <t>Maintenance Tools</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AWS authorizes, monitors, and audits all nonlocal maintenance on AWS-managed infrastructure via approved AWS-internal access paths with MFA and full session recording.</t>
+          <t>AWS controls, inspects, and sanitizes all maintenance tools entering AWS datacenter facilities per AWS physical security procedures.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: (a) all administrative access via Systems Manager Session Manager (no direct SSH/RDP), (b) MFA enforced on all administrative sessions, (c) session recording enabled and stored in tamper-resistant S3 with Object Lock, and (d) FIPS-validated transport for all administrative connections.</t>
+          <t>Customer is responsible for approving and controlling customer-side maintenance tools used against customer-managed resources, including Systems Manager Run Command documents, Session Manager preferences, third-party EDR maintenance agents, and any customer scripts with elevated privileges.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MA-5</t>
+          <t>MA-4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Personnel</t>
+          <t>Nonlocal Maintenance</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>AWS maintenance personnel undergo AWS Personnel Security screening per PS-3 (inherited) prior to access authorization.</t>
+          <t>AWS authorizes, monitors, and audits all nonlocal maintenance on AWS-managed infrastructure via approved AWS-internal access paths with MFA and full session recording.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vetting customer personnel authorized to perform maintenance on customer-managed AWS resources: background investigation per customer PS-3, designated maintenance role in IAM, documented authorization, and revocation upon role change or separation.</t>
+          <t>Customer is responsible for nonlocal maintenance of customer-managed resources: (a) all administrative access via Systems Manager Session Manager (no direct SSH/RDP), (b) MFA enforced on all administrative sessions, (c) session recording enabled and stored in tamper-resistant S3 with Object Lock, and (d) FIPS-validated transport for all administrative connections.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SA-9</t>
+          <t>MA-5</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>External System Services</t>
+          <t>Maintenance Personnel</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>AWS provides FedRAMP High authorized services within GovCloud; AWS publishes the FedRAMP authorization package, SOC reports, and ISO certifications via AWS Artifact for customer due-diligence review.</t>
+          <t>AWS maintenance personnel undergo AWS Personnel Security screening per PS-3 (inherited) prior to access authorization.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) assessing external (non-AWS) services used by customer workloads against customer security requirements, (b) documenting all customer-managed third-party connections and the data flows traversing them, (c) ensuring contractual security commitments from third-party providers, and (d) periodic re-assessment of external service authorizations.</t>
+          <t>Customer is responsible for vetting customer personnel authorized to perform maintenance on customer-managed AWS resources: background investigation per customer PS-3, designated maintenance role in IAM, documented authorization, and revocation upon role change or separation.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SC-1</t>
+          <t>SA-9</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>System and Communications Protection Policy and Procedures</t>
+          <t>External System Services</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>AWS maintains AWS-internal system and communications protection policy and procedures applicable to AWS-managed infrastructure, reviewed annually.</t>
+          <t>AWS provides FedRAMP High authorized services within GovCloud; AWS publishes the FedRAMP authorization package, SOC reports, and ISO certifications via AWS Artifact for customer due-diligence review.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and annually reviewing the customer-side system and communications protection policy and procedures, addressing customer-deployed network architecture, encryption requirements, and boundary protection design.</t>
+          <t>Customer is responsible for (a) assessing external (non-AWS) services used by customer workloads against customer security requirements, (b) documenting all customer-managed third-party connections and the data flows traversing them, (c) ensuring contractual security commitments from third-party providers, and (d) periodic re-assessment of external service authorizations.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SC-7</t>
+          <t>SC-1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Boundary Protection</t>
+          <t>System and Communications Protection Policy and Procedures</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>AWS provides VPC, Security Groups, Network ACLs, AWS WAF, AWS Shield, Network Firewall, Transit Gateway, and PrivateLink as boundary protection primitives. AWS protects the AWS service boundary at the service API layer.</t>
+          <t>AWS maintains AWS-internal system and communications protection policy and procedures applicable to AWS-managed infrastructure, reviewed annually.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for designing the customer VPC boundary architecture including (a) public/private subnet segmentation, (b) Security Group rules enforcing least-privilege traffic flows, (c) NACL rules at the subnet boundary, (d) WAF rules on internet-facing ALBs and API Gateway, (e) Network Firewall deployment for VPC-level egress filtering, and (f) enforcement of the customer-defined boundary between trust zones per the customer architecture.</t>
+          <t>Customer is responsible for developing, documenting, and annually reviewing the customer-side system and communications protection policy and procedures, addressing customer-deployed network architecture, encryption requirements, and boundary protection design.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SC-8</t>
+          <t>SC-7</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Transmission Confidentiality and Integrity</t>
+          <t>Boundary Protection</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>AWS encrypts data in transit between AWS services and across AWS regions using TLS 1.2 or higher with FIPS-validated cipher suites. AWS physically protects inter-datacenter dark fiber.</t>
+          <t>AWS provides VPC, Security Groups, Network ACLs, AWS WAF, AWS Shield, Network Firewall, Transit Gateway, and PrivateLink as boundary protection primitives. AWS protects the AWS service boundary at the service API layer.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints (ALB/NLB listeners, API Gateway, CloudFront distributions), (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access via redirect or policy, (d) ensuring application-layer TLS for service-to-service communication, and (e) using FIPS endpoints (-fips. suffix) where the customer system is FedRAMP- or FISMA-regulated.</t>
+          <t>Customer is responsible for designing the customer VPC boundary architecture including (a) public/private subnet segmentation, (b) Security Group rules enforcing least-privilege traffic flows, (c) NACL rules at the subnet boundary, (d) WAF rules on internet-facing ALBs and API Gateway, (e) Network Firewall deployment for VPC-level egress filtering, and (f) enforcement of the customer-defined boundary between trust zones per the customer architecture.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-8</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Key Establishment and Management</t>
+          <t>Transmission Confidentiality and Integrity</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>AWS manages keys for AWS-managed encryption (AWS-owned and AWS-managed KMS keys). AWS provides AWS KMS (FIPS 140-2 Level 2 validated HSMs) and AWS CloudHSM (FIPS 140-2 Level 3 validated single-tenant HSMs) for customer key management.</t>
+          <t>AWS encrypts data in transit between AWS services and across AWS regions using TLS 1.2 or higher with FIPS-validated cipher suites. AWS physically protects inter-datacenter dark fiber.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for managing customer-managed KMS CMKs and CloudHSM clusters where applicable: (a) key creation with appropriate key spec and usage, (b) automatic annual rotation enabled for symmetric CMKs, (c) IAM and key policies enforcing least-privilege key access, (d) CloudTrail logging of all key usage, and (e) scheduled deletion with appropriate waiting period prior to permanent removal.</t>
+          <t>Customer is responsible for (a) enforcing TLS 1.2+ on all customer-facing endpoints (ALB/NLB listeners, API Gateway, CloudFront distributions), (b) configuring only approved FIPS-validated cipher suites, (c) enforcing HTTPS-only access via redirect or policy, (d) ensuring application-layer TLS for service-to-service communication, and (e) using FIPS endpoints (-fips. suffix) where the customer system is FedRAMP- or FISMA-regulated.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SC-13</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Protection</t>
+          <t>Cryptographic Key Establishment and Management</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>AWS provides FIPS 140-2 validated cryptographic modules within GovCloud via AWS KMS (Level 2), AWS CloudHSM (Level 3), AWS Certificate Manager, and FIPS-validated service endpoints. NIAP-approved configurations available per service.</t>
+          <t>AWS manages keys for AWS-managed encryption (AWS-owned and AWS-managed KMS keys). AWS provides AWS KMS (FIPS 140-2 Level 2 validated HSMs) and AWS CloudHSM (FIPS 140-2 Level 3 validated single-tenant HSMs) for customer key management.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for using only FIPS 140-2 validated cryptographic implementations for all customer workloads: (a) enable FIPS service endpoints (-fips. suffix) for all customer service calls, (b) configure FIPS mode in customer EC2 guest operating systems where supported, (c) avoid non-FIPS algorithms in customer applications, and (d) document customer cryptographic implementations in the customer SSP.</t>
+          <t>Customer is responsible for managing customer-managed KMS CMKs and CloudHSM clusters where applicable: (a) key creation with appropriate key spec and usage, (b) automatic annual rotation enabled for symmetric CMKs, (c) IAM and key policies enforcing least-privilege key access, (d) CloudTrail logging of all key usage, and (e) scheduled deletion with appropriate waiting period prior to permanent removal.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SI-2</t>
+          <t>SC-13</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Flaw Remediation</t>
+          <t>Cryptographic Protection</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>AWS identifies and remediates flaws in AWS-managed services per AWS Vulnerability Management policy. AWS publishes service-level security bulletins via the AWS Security Bulletins page.</t>
+          <t>AWS provides FIPS 140-2 validated cryptographic modules within GovCloud via AWS KMS (Level 2), AWS CloudHSM (Level 3), AWS Certificate Manager, and FIPS-validated service endpoints. NIAP-approved configurations available per service.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS, container, and application patching via AWS Systems Manager Patch Manager, (b) Inspector findings remediation per customer-defined SLAs, (c) Critical CVEs remediated within 30 days of vendor disclosure, (d) High CVEs within 90 days, (e) CISA Known Exploited Vulnerabilities Catalog entries remediated within the BOD 22-01 mandated timeframe (typically 15 days for federal systems), and (f) documented exception process for any deviation.</t>
+          <t>Customer is responsible for using only FIPS 140-2 validated cryptographic implementations for all customer workloads: (a) enable FIPS service endpoints (-fips. suffix) for all customer service calls, (b) configure FIPS mode in customer EC2 guest operating systems where supported, (c) avoid non-FIPS algorithms in customer applications, and (d) document customer cryptographic implementations in the customer SSP.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SI-3</t>
+          <t>SI-2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Malicious Code Protection</t>
+          <t>Flaw Remediation</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>AWS protects AWS-managed infrastructure against malicious code via AWS-internal endpoint protection and AWS-internal SOC monitoring.</t>
+          <t>AWS identifies and remediates flaws in AWS-managed services per AWS Vulnerability Management policy. AWS publishes service-level security bulletins via the AWS Security Bulletins page.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for deploying malicious code protection on customer workloads: (a) anti-malware on customer EC2 / EKS / ECS workloads via vendor EDR or ClamAV, (b) Amazon GuardDuty Malware Protection enabled across all accounts, (c) signature and engine updates within 24 hours of vendor release, and (d) remediation of detections per customer IR-4.</t>
+          <t>Customer is responsible for remediating flaws in customer-managed components: (a) guest OS, container, and application patching via AWS Systems Manager Patch Manager, (b) Inspector findings remediation per customer-defined SLAs, (c) Critical CVEs remediated within 30 days of vendor disclosure, (d) High CVEs within 90 days, (e) CISA Known Exploited Vulnerabilities Catalog entries remediated within the BOD 22-01 mandated timeframe (typically 15 days for federal systems), and (f) documented exception process for any deviation.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SI-4</t>
+          <t>SI-3</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>System Monitoring</t>
+          <t>Malicious Code Protection</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>AWS monitors AWS-managed infrastructure via AWS-internal SOC tooling with 24x7 coverage and automated alerting.</t>
+          <t>AWS protects AWS-managed infrastructure against malicious code via AWS-internal endpoint protection and AWS-internal SOC monitoring.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for monitoring customer-deployed workloads via (a) CloudWatch metrics and alarms, (b) Amazon GuardDuty across all accounts and regions, (c) AWS Security Hub for cross-service finding aggregation, (d) AWS Inspector for vulnerability assessment, (e) Amazon Macie for sensitive-data discovery in S3, and (f) customer SIEM integration via Kinesis Data Firehose or partner connector. Alerts triaged per IR-4.</t>
+          <t>Customer is responsible for deploying malicious code protection on customer workloads: (a) anti-malware on customer EC2 / EKS / ECS workloads via vendor EDR or ClamAV, (b) Amazon GuardDuty Malware Protection enabled across all accounts, (c) signature and engine updates within 24 hours of vendor release, and (d) remediation of detections per customer IR-4.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MP-4</t>
+          <t>SI-4</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Media Storage</t>
+          <t>System Monitoring</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>AWS physically secures and controls access to storage media within AWS datacenter facilities per AWS Physical Security policy.</t>
+          <t>AWS monitors AWS-managed infrastructure via AWS-internal SOC tooling with 24x7 coverage and automated alerting.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for protecting customer logical media: (a) data classification labeling via S3 object tags, (b) S3 bucket policies denying public access with S3 Block Public Access at account and bucket level, (c) encryption-at-rest for all customer media (EBS, S3, RDS, DynamoDB) using customer-managed KMS keys, and (d) MFA Delete on critical S3 buckets.</t>
+          <t>Customer is responsible for monitoring customer-deployed workloads via (a) CloudWatch metrics and alarms, (b) Amazon GuardDuty across all accounts and regions, (c) AWS Security Hub for cross-service finding aggregation, (d) AWS Inspector for vulnerability assessment, (e) Amazon Macie for sensitive-data discovery in S3, and (f) customer SIEM integration via Kinesis Data Firehose or partner connector. Alerts triaged per IR-4.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1915,76 +1915,76 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MP-6</t>
+          <t>MP-4</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Media Sanitization</t>
+          <t>Media Storage</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS GovCloud customer service offering for this system: AWS performs NIST SP 800-88 cryptographic erasure of the customer-managed storage media plane (EBS/S3 key destruction) as a provider operation; there is no separate customer media-sanitization action on this enclave.</t>
+          <t>AWS physically secures and controls access to storage media within AWS datacenter facilities per AWS Physical Security policy.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer on AWS GovCloud. The customer retains no media-sanitization implementation or compensating-control responsibility for this enclave; sanitization is provider-performed via cryptographic erasure.</t>
+          <t>Customer is responsible for protecting customer logical media: (a) data classification labeling via S3 object tags, (b) S3 bucket policies denying public access with S3 Block Public Access at account and bucket level, (c) encryption-at-rest for all customer media (EBS, S3, RDS, DynamoDB) using customer-managed KMS keys, and (d) MFA Delete on critical S3 buckets.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AC-17</t>
+          <t>MP-6</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Remote Access</t>
+          <t>Media Sanitization</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>AWS provides the network primitives (Client VPN, Verified Access, Security Groups, IAM) but does not configure or operate the customer's remote-access policy or endpoints.</t>
+          <t>Not applicable to the AWS GovCloud customer service offering for this system: AWS performs NIST SP 800-88 cryptographic erasure of the customer-managed storage media plane (EBS/S3 key destruction) as a provider operation; there is no separate customer media-sanitization action on this enclave.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for authorizing remote access prior to connection and enforcing approved methods: AWS Client VPN with certificate + IdP authentication, conditional-access rules, session logging to CloudWatch, and periodic review of remote-access entitlements.</t>
+          <t>Not applicable to customer on AWS GovCloud. The customer retains no media-sanitization implementation or compensating-control responsibility for this enclave; sanitization is provider-performed via cryptographic erasure.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Not Implemented</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AT-1</t>
+          <t>AC-17</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Awareness and Training Policy and Procedures</t>
+          <t>Remote Access</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
+          <t>AWS provides the network primitives (Client VPN, Verified Access, Security Groups, IAM) but does not configure or operate the customer's remote-access policy or endpoints.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
+          <t>Customer is responsible for authorizing remote access prior to connection and enforcing approved methods: AWS Client VPN with certificate + IdP authentication, conditional-access rules, session logging to CloudWatch, and periodic review of remote-access entitlements.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AT-2</t>
+          <t>AT-1</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Literacy Training and Awareness</t>
+          <t>Awareness and Training Policy and Procedures</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side awareness and training policy independently.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
+          <t>Customer is responsible for developing, documenting, disseminating, reviewing, and updating the customer security awareness and training policy and supporting procedures applicable to all customer personnel with access to customer information systems.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AT-3</t>
+          <t>AT-2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Role-Based Training</t>
+          <t>Literacy Training and Awareness</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
+          <t>Customer is responsible for providing security literacy training and awareness to all customer information system users on initial access, annually thereafter, and following any significant change to the system environment, including role-based content per the customer training program.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>AT-3</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>System Security and Privacy Plans</t>
+          <t>Role-Based Training</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
+          <t>Customer is responsible for providing role-based security training to customer personnel with significant security responsibilities (cloud administrators, security engineers, developers with production access) prior to authorizing access and annually thereafter.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PL-4</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Rules of Behavior</t>
+          <t>System Security and Privacy Plans</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary.</t>
+          <t>Not applicable to the AWS service boundary. Customer maintains the customer-side System Security Plan independently.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
+          <t>Customer is responsible for developing, documenting, and maintaining the customer System Security Plan covering customer-deployed workloads, customer responsibilities, and the explicit inheritance and shared responsibility relationships with AWS per this CRM.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PM-1</t>
+          <t>PL-4</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Information Security Program Plan</t>
+          <t>Rules of Behavior</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
+          <t>Customer is responsible for establishing and enforcing rules of behavior for customer users with access to customer-managed AWS resources, including acknowledgment prior to access authorization.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PM-9</t>
+          <t>PM-1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Strategy</t>
+          <t>Information Security Program Plan</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
+          <t>Customer is responsible for establishing and maintaining the customer Information Security Program Plan, including customer governance, risk, compliance functions, and senior agency information security officer designation.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RA-3</t>
+          <t>PM-9</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Management Strategy</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
+          <t>Customer is responsible for developing and implementing the customer Risk Management Strategy, including risk tolerance levels for customer-managed workloads in AWS GovCloud and risk framing for the inherited and shared portions of the AWS shared responsibility model.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2235,12 +2235,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RA-5</t>
+          <t>RA-3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Monitoring and Scanning</t>
+          <t>Risk Assessment</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
+          <t>Not applicable to the AWS service boundary.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
+          <t>Customer is responsible for conducting risk assessments of customer-deployed information systems at minimum annually and following any significant change, incorporating the AWS shared responsibility model and the customer-specific threat landscape.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2267,62 +2267,94 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PE-10</t>
+          <t>RA-5</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Emergency Shutoff</t>
+          <t>Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+          <t>Not applicable to the AWS service boundary. AWS scans AWS-managed infrastructure independently per the AWS Vulnerability Management program.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+          <t>Customer is responsible for vulnerability scanning of customer-deployed workloads via Amazon Inspector (EC2, ECR, Lambda), customer third-party scanners (Tenable Nessus, Qualys, Rapid7), and remediating findings per customer-defined SLAs aligned to SI-2.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Not Implemented</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>PE-10</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Emergency Shutoff</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to AWS GovCloud (US) customer service offering. AWS datacenter emergency power shutoff is an AWS-internal facility control not exposed to customer interaction.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable to customer. Customer has no role in datacenter emergency shutoff procedures and no requirement to implement an equivalent compensating control.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>PE-11</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Emergency Power</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Not applicable to AWS GovCloud (US) customer service offering. AWS provides datacenter emergency power (UPS, generators, fuel reserves) as an internal infrastructure control.</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Not applicable to customer. AWS GovCloud datacenter emergency power implementation is fully internal to AWS facilities; customer has no implementation or compensating-control responsibility.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>
